--- a/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
+++ b/01_analyses_mask-ONEland/results/SoIB_summaries.xlsx
@@ -591,10 +591,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -602,10 +602,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -700,7 +700,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -708,7 +708,7 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -716,7 +716,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +745,7 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -753,7 +753,7 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>24</v>
@@ -764,7 +764,7 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>22</v>
@@ -813,7 +813,7 @@
         <v>89</v>
       </c>
       <c r="C2">
-        <v>84</v>
+        <v>83.2</v>
       </c>
       <c r="D2">
         <v>89</v>
@@ -830,7 +830,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -838,10 +838,10 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>12.3</v>
+        <v>13.1</v>
       </c>
       <c r="D4">
         <v>3</v>
